--- a/evaluation/gemini_domain.xlsx
+++ b/evaluation/gemini_domain.xlsx
@@ -349,7 +349,7 @@
         <v>0.33909843382614646</v>
       </c>
       <c r="D1" s="0" t="n">
-        <v>0.3538095238095238</v>
+        <v>0.6505889724310777</v>
       </c>
     </row>
     <row r="2">
@@ -401,7 +401,7 @@
         <v>0.4195918749292481</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>0.4785714285714285</v>
+        <v>0.7392857142857142</v>
       </c>
     </row>
     <row r="5">
@@ -417,7 +417,7 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>0.45</v>
+        <v>0.725</v>
       </c>
     </row>
     <row r="6">
@@ -433,7 +433,7 @@
         <v>0.0</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>0.01936026936026936</v>
+        <v>0.43275705775705775</v>
       </c>
     </row>
     <row r="7">
@@ -449,7 +449,7 @@
         <v>0.0</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>0.125</v>
+        <v>0.4910714285714286</v>
       </c>
     </row>
     <row r="8">
@@ -481,7 +481,7 @@
         <v>0.08212301166528897</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>0.09999999999999998</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="10">
@@ -497,7 +497,7 @@
         <v>0.20364642070933447</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>0.26666666666666666</v>
+        <v>0.6333333333333333</v>
       </c>
     </row>
     <row r="11">
@@ -513,7 +513,7 @@
         <v>0.7039142796459298</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>0.6722222222222222</v>
+        <v>0.836111111111111</v>
       </c>
     </row>
     <row r="12">
@@ -529,7 +529,7 @@
         <v>0.0</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>0.0</v>
+        <v>0.45918367346938777</v>
       </c>
     </row>
     <row r="13">
@@ -545,7 +545,7 @@
         <v>0.9920413366950351</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>0.28269230769230763</v>
+        <v>0.5545405982905982</v>
       </c>
     </row>
     <row r="14">
@@ -561,7 +561,7 @@
         <v>0.25</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>0.46428571428571425</v>
+        <v>0.7008928571428571</v>
       </c>
     </row>
     <row r="15">
@@ -577,7 +577,7 @@
         <v>0.21285178621068154</v>
       </c>
       <c r="D15" s="0" t="n">
-        <v>0.25</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         <v>0.35079533020331677</v>
       </c>
       <c r="D16" s="0" t="n">
-        <v>0.2962962962962963</v>
+        <v>0.4814814814814815</v>
       </c>
     </row>
     <row r="17">
@@ -609,7 +609,7 @@
         <v>0.8197147287353861</v>
       </c>
       <c r="D17" s="0" t="n">
-        <v>0.3888888888888889</v>
+        <v>0.6527777777777778</v>
       </c>
     </row>
     <row r="18">
@@ -625,7 +625,7 @@
         <v>0.2651255816299077</v>
       </c>
       <c r="D18" s="0" t="n">
-        <v>0.2784382284382284</v>
+        <v>0.6392191142191141</v>
       </c>
     </row>
     <row r="19">
@@ -641,7 +641,7 @@
         <v>0.22003794382723907</v>
       </c>
       <c r="D19" s="0" t="n">
-        <v>0.3666666666666667</v>
+        <v>0.6694444444444445</v>
       </c>
     </row>
     <row r="20">
@@ -657,7 +657,7 @@
         <v>0.9860332223644985</v>
       </c>
       <c r="D20" s="0" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.40690208667736755</v>
       </c>
     </row>
     <row r="21">
@@ -673,7 +673,7 @@
         <v>0.49718372032830144</v>
       </c>
       <c r="D21" s="0" t="n">
-        <v>0.36005291005291</v>
+        <v>0.6256786289394984</v>
       </c>
     </row>
     <row r="22">
@@ -689,7 +689,7 @@
         <v>0.36559615122360445</v>
       </c>
       <c r="D22" s="0" t="n">
-        <v>0.4</v>
+        <v>0.5928571428571429</v>
       </c>
     </row>
     <row r="23">
@@ -705,7 +705,7 @@
         <v>0.9591713936340666</v>
       </c>
       <c r="D23" s="0" t="n">
-        <v>0.3522727272727273</v>
+        <v>0.5584893048128342</v>
       </c>
     </row>
     <row r="24">
@@ -721,7 +721,7 @@
         <v>0.2628338436602802</v>
       </c>
       <c r="D24" s="0" t="n">
-        <v>0.25</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="25">
@@ -737,7 +737,7 @@
         <v>0.21109099014371072</v>
       </c>
       <c r="D25" s="0" t="n">
-        <v>0.25476190476190474</v>
+        <v>0.6273809523809524</v>
       </c>
     </row>
   </sheetData>

--- a/evaluation/gemini_domain.xlsx
+++ b/evaluation/gemini_domain.xlsx
@@ -349,7 +349,7 @@
         <v>0.33909843382614646</v>
       </c>
       <c r="D1" s="0" t="n">
-        <v>0.6505889724310777</v>
+        <v>0.33518796992481203</v>
       </c>
     </row>
     <row r="2">
@@ -401,7 +401,7 @@
         <v>0.4195918749292481</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>0.7392857142857142</v>
+        <v>0.4785714285714285</v>
       </c>
     </row>
     <row r="5">
@@ -417,7 +417,7 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>0.725</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="6">
@@ -433,7 +433,7 @@
         <v>0.0</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>0.43275705775705775</v>
+        <v>0.01638176638176638</v>
       </c>
     </row>
     <row r="7">
@@ -449,7 +449,7 @@
         <v>0.0</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>0.4910714285714286</v>
+        <v>0.10714285714285715</v>
       </c>
     </row>
     <row r="8">
@@ -481,7 +481,7 @@
         <v>0.08212301166528897</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>0.55</v>
+        <v>0.09999999999999998</v>
       </c>
     </row>
     <row r="10">
@@ -497,7 +497,7 @@
         <v>0.20364642070933447</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>0.6333333333333333</v>
+        <v>0.26666666666666666</v>
       </c>
     </row>
     <row r="11">
@@ -513,7 +513,7 @@
         <v>0.7039142796459298</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>0.836111111111111</v>
+        <v>0.6722222222222222</v>
       </c>
     </row>
     <row r="12">
@@ -529,7 +529,7 @@
         <v>0.0</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>0.45918367346938777</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="13">
@@ -545,7 +545,7 @@
         <v>0.9920413366950351</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>0.5545405982905982</v>
+        <v>0.233613782051282</v>
       </c>
     </row>
     <row r="14">
@@ -561,7 +561,7 @@
         <v>0.25</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>0.7008928571428571</v>
+        <v>0.4352678571428571</v>
       </c>
     </row>
     <row r="15">
@@ -577,7 +577,7 @@
         <v>0.21285178621068154</v>
       </c>
       <c r="D15" s="0" t="n">
-        <v>0.625</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         <v>0.35079533020331677</v>
       </c>
       <c r="D16" s="0" t="n">
-        <v>0.4814814814814815</v>
+        <v>0.19753086419753088</v>
       </c>
     </row>
     <row r="17">
@@ -609,7 +609,7 @@
         <v>0.8197147287353861</v>
       </c>
       <c r="D17" s="0" t="n">
-        <v>0.6527777777777778</v>
+        <v>0.35648148148148145</v>
       </c>
     </row>
     <row r="18">
@@ -625,7 +625,7 @@
         <v>0.2651255816299077</v>
       </c>
       <c r="D18" s="0" t="n">
-        <v>0.6392191142191141</v>
+        <v>0.2784382284382284</v>
       </c>
     </row>
     <row r="19">
@@ -641,7 +641,7 @@
         <v>0.22003794382723907</v>
       </c>
       <c r="D19" s="0" t="n">
-        <v>0.6694444444444445</v>
+        <v>0.3564814814814815</v>
       </c>
     </row>
     <row r="20">
@@ -657,7 +657,7 @@
         <v>0.9860332223644985</v>
       </c>
       <c r="D20" s="0" t="n">
-        <v>0.40690208667736755</v>
+        <v>0.1508828250401284</v>
       </c>
     </row>
     <row r="21">
@@ -673,7 +673,7 @@
         <v>0.49718372032830144</v>
       </c>
       <c r="D21" s="0" t="n">
-        <v>0.6256786289394984</v>
+        <v>0.3209167241775937</v>
       </c>
     </row>
     <row r="22">
@@ -689,7 +689,7 @@
         <v>0.36559615122360445</v>
       </c>
       <c r="D22" s="0" t="n">
-        <v>0.5928571428571429</v>
+        <v>0.3142857142857143</v>
       </c>
     </row>
     <row r="23">
@@ -705,7 +705,7 @@
         <v>0.9591713936340666</v>
       </c>
       <c r="D23" s="0" t="n">
-        <v>0.5584893048128342</v>
+        <v>0.26938502673796794</v>
       </c>
     </row>
     <row r="24">
@@ -721,7 +721,7 @@
         <v>0.2628338436602802</v>
       </c>
       <c r="D24" s="0" t="n">
-        <v>0.625</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="25">
@@ -737,7 +737,7 @@
         <v>0.21109099014371072</v>
       </c>
       <c r="D25" s="0" t="n">
-        <v>0.6273809523809524</v>
+        <v>0.25476190476190474</v>
       </c>
     </row>
   </sheetData>
